--- a/converted/tozalangan/chinobod/Sentabr 10 kunlik/Elektr Podstansiyalar.xlsx
+++ b/converted/tozalangan/chinobod/Sentabr 10 kunlik/Elektr Podstansiyalar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>Podstansiyalar Sentabr (1–10) Holatiga Ko'ra</t>
   </si>
@@ -55,6 +55,9 @@
     <t>Quvvati (KVA) (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
   </si>
   <si>
     <t>110 kV</t>
+  </si>
+  <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi</t>
   </si>
   <si>
     <t>chinobod/Elektr Podstansiyalar.xlsx [Sentabr], 3-qator</t>
@@ -516,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -525,10 +531,10 @@
     <col min="6" max="7" width="16" style="2" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="14" width="26" customWidth="1"/>
+    <col min="10" max="15" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -545,8 +551,9 @@
       <c r="L1"/>
       <c r="M1"/>
       <c r="N1"/>
+      <c r="O1"/>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" ht="45" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -589,10 +596,13 @@
       <c r="N2" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="O2" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1">
         <v>1080998</v>
@@ -604,7 +614,7 @@
         <v>172959.68</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2">
         <v>40.866486</v>
@@ -613,27 +623,30 @@
         <v>71.968873</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1">
         <v>882000</v>
@@ -645,7 +658,7 @@
         <v>141120</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2">
         <v>40.850754</v>
@@ -654,27 +667,30 @@
         <v>72.04806</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
